--- a/docs/assets/面包板.xlsx
+++ b/docs/assets/面包板.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reed38121ef5b4e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Refcd75ba2a1c4e7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="Rcfbf8d48f4e64fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc30e3bfef4db436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" r:id="Rfb01dc66eb1f47ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" r:id="Rbd93a7e15ee043aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -58,7 +58,7 @@
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="22">
+  <x:fonts count="25">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -179,8 +179,24 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="43">
+  <x:fills count="48">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -390,6 +406,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF1F5F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEE2E2"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -638,7 +679,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -712,6 +753,36 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="44" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="47" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -969,11 +1040,11 @@
     <x:col min="15" max="15" width="4" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="10" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="17" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="83" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="3" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1019,14 +1090,14 @@
       <x:c r="Q1" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S1" s="20" t="str">
+      <x:c r="S1" s="33" t="str">
         <x:v>接线说明</x:v>
       </x:c>
-      <x:c r="T1" s="20" t="str">
-        <x:v>双 TB6612FNG 面包板孔位</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="48" customHeight="1">
+      <x:c r="T1" s="33" t="str">
+        <x:v>双 TB6612FNG 两线法（2026-10-06）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="10" t="str">
         <x:v>3.3V</x:v>
       </x:c>
@@ -1051,7 +1122,8 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P2" s="14" t="str">
-        <x:v>5V预留</x:v>
+        <x:v>留空
+无电</x:v>
       </x:c>
       <x:c r="Q2" s="12" t="str">
         <x:v>GND</x:v>
@@ -1060,17 +1132,17 @@
         <x:v>适用范围</x:v>
       </x:c>
       <x:c r="T2" s="22" t="str">
-        <x:v>现有 ESP32 单独调底盘。先断开投掷驱动控制线和 PS2 信号线；不能与旧 GPIO 接法叠加。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="48" customHeight="1">
+        <x:v>经典 ESP32，GPIO16/17 可用。8 根 IN + GPIO33 STBY，共 9 根；无需扩展器。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="46" customHeight="1">
       <x:c r="A3" s="10" t="str">
         <x:v>ESP32
 3V3</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>逻辑
-共地</x:v>
+        <x:v>ESP32
+GND</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>2</x:v>
@@ -1095,57 +1167,58 @@
         <x:v>读图方式</x:v>
       </x:c>
       <x:c r="T3" s="22" t="str">
-        <x:v>顶行 a–j 是物理孔列；左右 1–30 是物理排号。例如 a3 为 Excel D4，e3 为 H4。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="48" customHeight="1">
+        <x:v>a–j 为物理孔列，1–30 为物理排号；a3=Excel D4。模块放板旁，按信号名接线。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="46" customHeight="1">
       <x:c r="A4" s="10" t="str">
         <x:v>D1
 VCC</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>地轨
-桥接Q</x:v>
+        <x:v>桥接
+右−3</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D4" s="6" t="str">
-        <x:v>GPIO25</x:v>
-      </x:c>
-      <x:c r="E4" s="2"/>
-      <x:c r="F4" s="2"/>
-      <x:c r="G4" s="2"/>
-      <x:c r="H4" s="6" t="str">
+      <x:c r="D4" s="27" t="str">
+        <x:v>GPIO16</x:v>
+      </x:c>
+      <x:c r="E4" s="26"/>
+      <x:c r="F4" s="26"/>
+      <x:c r="G4" s="26"/>
+      <x:c r="H4" s="27" t="str">
         <x:v>D1
-PWMA</x:v>
+AIN1</x:v>
       </x:c>
       <x:c r="I4" s="1"/>
-      <x:c r="J4" s="7" t="str">
-        <x:v>GPIO27</x:v>
-      </x:c>
-      <x:c r="K4" s="2"/>
-      <x:c r="L4" s="2"/>
-      <x:c r="M4" s="2"/>
-      <x:c r="N4" s="7" t="str">
+      <x:c r="J4" s="28" t="str">
+        <x:v>GPIO23</x:v>
+      </x:c>
+      <x:c r="K4" s="26"/>
+      <x:c r="L4" s="26"/>
+      <x:c r="M4" s="26"/>
+      <x:c r="N4" s="28" t="str">
         <x:v>D2
-PWMA</x:v>
+AIN1</x:v>
       </x:c>
       <x:c r="O4" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="P4" s="15"/>
       <x:c r="Q4" s="12" t="str">
-        <x:v>桥接B</x:v>
+        <x:v>桥接
+左−3</x:v>
       </x:c>
       <x:c r="S4" s="23" t="str">
         <x:v>左板 D1</x:v>
       </x:c>
       <x:c r="T4" s="22" t="str">
-        <x:v>A 通道 AO1/AO2 接左前；B 通道 BO1/BO2 接左后。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="48" customHeight="1">
+        <x:v>AO1/AO2 接左前 FL；BO1/BO2 接左后 RL。IN：16/17、18/19。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="10" t="str">
         <x:v>D2
 VCC</x:v>
@@ -1154,24 +1227,24 @@
       <x:c r="C5" s="1">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D5" s="6" t="str">
+      <x:c r="D5" s="27" t="str">
         <x:v>GPIO17</x:v>
       </x:c>
-      <x:c r="E5" s="2"/>
-      <x:c r="F5" s="2"/>
-      <x:c r="G5" s="2"/>
-      <x:c r="H5" s="6" t="str">
+      <x:c r="E5" s="26"/>
+      <x:c r="F5" s="26"/>
+      <x:c r="G5" s="26"/>
+      <x:c r="H5" s="27" t="str">
         <x:v>D1
 AIN2</x:v>
       </x:c>
       <x:c r="I5" s="1"/>
-      <x:c r="J5" s="7" t="str">
+      <x:c r="J5" s="28" t="str">
         <x:v>GPIO32</x:v>
       </x:c>
-      <x:c r="K5" s="2"/>
-      <x:c r="L5" s="2"/>
-      <x:c r="M5" s="2"/>
-      <x:c r="N5" s="7" t="str">
+      <x:c r="K5" s="26"/>
+      <x:c r="L5" s="26"/>
+      <x:c r="M5" s="26"/>
+      <x:c r="N5" s="28" t="str">
         <x:v>D2
 AIN2</x:v>
       </x:c>
@@ -1184,35 +1257,35 @@
         <x:v>右板 D2</x:v>
       </x:c>
       <x:c r="T5" s="22" t="str">
-        <x:v>A 通道 AO1/AO2 接右前；B 通道 BO1/BO2 接右后。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
+        <x:v>AO1/AO2 接右前 FR；BO1/BO2 接右后 RR。IN：23/32、15/5。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="11"/>
       <x:c r="B6" s="13"/>
       <x:c r="C6" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="str">
-        <x:v>GPIO16</x:v>
-      </x:c>
-      <x:c r="E6" s="2"/>
-      <x:c r="F6" s="2"/>
-      <x:c r="G6" s="2"/>
-      <x:c r="H6" s="6" t="str">
+      <x:c r="D6" s="27" t="str">
+        <x:v>GPIO18</x:v>
+      </x:c>
+      <x:c r="E6" s="26"/>
+      <x:c r="F6" s="26"/>
+      <x:c r="G6" s="26"/>
+      <x:c r="H6" s="27" t="str">
         <x:v>D1
-AIN1</x:v>
+BIN1</x:v>
       </x:c>
       <x:c r="I6" s="1"/>
-      <x:c r="J6" s="7" t="str">
-        <x:v>GPIO23</x:v>
-      </x:c>
-      <x:c r="K6" s="2"/>
-      <x:c r="L6" s="2"/>
-      <x:c r="M6" s="2"/>
-      <x:c r="N6" s="7" t="str">
+      <x:c r="J6" s="28" t="str">
+        <x:v>GPIO15</x:v>
+      </x:c>
+      <x:c r="K6" s="26"/>
+      <x:c r="L6" s="26"/>
+      <x:c r="M6" s="26"/>
+      <x:c r="N6" s="28" t="str">
         <x:v>D2
-AIN1</x:v>
+BIN1</x:v>
       </x:c>
       <x:c r="O6" s="1">
         <x:v>5</x:v>
@@ -1223,41 +1296,35 @@
         <x:v>同排连通</x:v>
       </x:c>
       <x:c r="T6" s="22" t="str">
-        <x:v>先测 a–e 同排相通、f–j 同排相通、中央隔槽不通；电源轨分段时同电压轨桥接。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="48" customHeight="1">
+        <x:v>断电测 a–e、f–j 各自相通，跨槽不通。电源轨分段时仅桥接同电位的两段。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="11"/>
       <x:c r="B7" s="13"/>
       <x:c r="C7" s="1">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
-        <x:v>GPIO4</x:v>
-      </x:c>
-      <x:c r="E7" s="8" t="str">
+      <x:c r="D7" s="27" t="str">
+        <x:v>GPIO19</x:v>
+      </x:c>
+      <x:c r="E7" s="25"/>
+      <x:c r="F7" s="25"/>
+      <x:c r="G7" s="26"/>
+      <x:c r="H7" s="27" t="str">
         <x:v>D1
-STBY</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str">
-        <x:v>10kΩ
-到地轨</x:v>
-      </x:c>
-      <x:c r="G7" s="2"/>
-      <x:c r="H7" s="8" t="str">
-        <x:v>跳线
-到f6</x:v>
+BIN2</x:v>
       </x:c>
       <x:c r="I7" s="1"/>
-      <x:c r="J7" s="7" t="str">
-        <x:v>e6跳线</x:v>
-      </x:c>
-      <x:c r="K7" s="2"/>
-      <x:c r="L7" s="2"/>
-      <x:c r="M7" s="2"/>
-      <x:c r="N7" s="7" t="str">
+      <x:c r="J7" s="28" t="str">
+        <x:v>GPIO5</x:v>
+      </x:c>
+      <x:c r="K7" s="26"/>
+      <x:c r="L7" s="26"/>
+      <x:c r="M7" s="26"/>
+      <x:c r="N7" s="28" t="str">
         <x:v>D2
-STBY</x:v>
+BIN2</x:v>
       </x:c>
       <x:c r="O7" s="1">
         <x:v>6</x:v>
@@ -1265,38 +1332,47 @@
       <x:c r="P7" s="15"/>
       <x:c r="Q7" s="13"/>
       <x:c r="S7" s="23" t="str">
-        <x:v>STBY</x:v>
+        <x:v>STBY 第7排</x:v>
       </x:c>
       <x:c r="T7" s="22" t="str">
-        <x:v>GPIO4 接 a6；D1 STBY 接 b6，D2 STBY 接 j6；e6–f6 跳线；c6 经 10kΩ 到 GND。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="48" customHeight="1">
+        <x:v>GPIO33→a7；b7→D1 STBY；e7–f7桥接；j7→D2 STBY；c7经10kΩ→左−第7孔。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="11"/>
-      <x:c r="B8" s="13"/>
+      <x:c r="B8" s="13" t="str">
+        <x:v>10kΩ
+另一端</x:v>
+      </x:c>
       <x:c r="C8" s="1">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
-        <x:v>GPIO18</x:v>
-      </x:c>
-      <x:c r="E8" s="2"/>
-      <x:c r="F8" s="2"/>
-      <x:c r="G8" s="2"/>
-      <x:c r="H8" s="6" t="str">
+      <x:c r="D8" s="29" t="str">
+        <x:v>GPIO33</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="str">
         <x:v>D1
-BIN1</x:v>
+STBY</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="str">
+        <x:v>10kΩ
+到左−7</x:v>
+      </x:c>
+      <x:c r="G8" s="30"/>
+      <x:c r="H8" s="29" t="str">
+        <x:v>跳线
+到f7</x:v>
       </x:c>
       <x:c r="I8" s="1"/>
-      <x:c r="J8" s="7" t="str">
-        <x:v>GPIO33</x:v>
-      </x:c>
-      <x:c r="K8" s="2"/>
-      <x:c r="L8" s="2"/>
-      <x:c r="M8" s="2"/>
-      <x:c r="N8" s="7" t="str">
+      <x:c r="J8" s="29" t="str">
+        <x:v>e7跳线</x:v>
+      </x:c>
+      <x:c r="K8" s="30"/>
+      <x:c r="L8" s="30"/>
+      <x:c r="M8" s="30"/>
+      <x:c r="N8" s="29" t="str">
         <x:v>D2
-BIN1</x:v>
+STBY</x:v>
       </x:c>
       <x:c r="O8" s="1">
         <x:v>7</x:v>
@@ -1304,38 +1380,42 @@
       <x:c r="P8" s="15"/>
       <x:c r="Q8" s="13"/>
       <x:c r="S8" s="23" t="str">
-        <x:v>3.3V 轨</x:v>
+        <x:v>左 + 轨</x:v>
       </x:c>
       <x:c r="T8" s="22" t="str">
-        <x:v>左 + 轨：ESP32 3V3、D1 VCC、D2 VCC。各线占独立孔，整轨同电位。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="11"/>
+        <x:v>3.3V。第2孔接3V3，第3/4孔接D1/D2 VCC；第8/9/10/11孔分别到a8/a9/f8/f9。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
+      <x:c r="A9" s="11" t="str">
+        <x:v>到a8</x:v>
+      </x:c>
       <x:c r="B9" s="13"/>
       <x:c r="C9" s="1">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
-        <x:v>GPIO19</x:v>
-      </x:c>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
-      <x:c r="G9" s="2"/>
-      <x:c r="H9" s="6" t="str">
+      <x:c r="D9" s="31" t="str">
+        <x:v>左+8
+3.3V</x:v>
+      </x:c>
+      <x:c r="E9" s="26"/>
+      <x:c r="F9" s="26"/>
+      <x:c r="G9" s="26"/>
+      <x:c r="H9" s="31" t="str">
         <x:v>D1
-BIN2</x:v>
+PWMA</x:v>
       </x:c>
       <x:c r="I9" s="1"/>
-      <x:c r="J9" s="7" t="str">
-        <x:v>GPIO13</x:v>
-      </x:c>
-      <x:c r="K9" s="2"/>
-      <x:c r="L9" s="2"/>
-      <x:c r="M9" s="2"/>
-      <x:c r="N9" s="7" t="str">
+      <x:c r="J9" s="31" t="str">
+        <x:v>左+10
+3.3V</x:v>
+      </x:c>
+      <x:c r="K9" s="26"/>
+      <x:c r="L9" s="26"/>
+      <x:c r="M9" s="26"/>
+      <x:c r="N9" s="31" t="str">
         <x:v>D2
-BIN2</x:v>
+PWMA</x:v>
       </x:c>
       <x:c r="O9" s="1">
         <x:v>8</x:v>
@@ -1343,36 +1423,40 @@
       <x:c r="P9" s="15"/>
       <x:c r="Q9" s="13"/>
       <x:c r="S9" s="23" t="str">
-        <x:v>GND 轨</x:v>
+        <x:v>逻辑地轨</x:v>
       </x:c>
       <x:c r="T9" s="22" t="str">
-        <x:v>左 − 和右 − 用跳线桥接，连 ESP32 GND、公共地端子。只分配逻辑地。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="11"/>
+        <x:v>左−第2孔接ESP32 GND，第3孔桥接右−第3孔，第12孔接公共地端子。电机回流不经地轨。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
+      <x:c r="A10" s="11" t="str">
+        <x:v>到a9</x:v>
+      </x:c>
       <x:c r="B10" s="13"/>
       <x:c r="C10" s="1">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
-        <x:v>GPIO26</x:v>
-      </x:c>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="6" t="str">
+      <x:c r="D10" s="31" t="str">
+        <x:v>左+9
+3.3V</x:v>
+      </x:c>
+      <x:c r="E10" s="26"/>
+      <x:c r="F10" s="26"/>
+      <x:c r="G10" s="26"/>
+      <x:c r="H10" s="31" t="str">
         <x:v>D1
 PWMB</x:v>
       </x:c>
       <x:c r="I10" s="1"/>
-      <x:c r="J10" s="7" t="str">
-        <x:v>GPIO14</x:v>
-      </x:c>
-      <x:c r="K10" s="2"/>
-      <x:c r="L10" s="2"/>
-      <x:c r="M10" s="2"/>
-      <x:c r="N10" s="7" t="str">
+      <x:c r="J10" s="31" t="str">
+        <x:v>左+11
+3.3V</x:v>
+      </x:c>
+      <x:c r="K10" s="26"/>
+      <x:c r="L10" s="26"/>
+      <x:c r="M10" s="26"/>
+      <x:c r="N10" s="31" t="str">
         <x:v>D2
 PWMB</x:v>
       </x:c>
@@ -1382,14 +1466,16 @@
       <x:c r="P10" s="15"/>
       <x:c r="Q10" s="13"/>
       <x:c r="S10" s="23" t="str">
-        <x:v>5V 轨</x:v>
+        <x:v>右 + 轨</x:v>
       </x:c>
       <x:c r="T10" s="22" t="str">
-        <x:v>右 + 轨预留 5V，目前不供电。绝不与左 3.3V 轨桥接。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="11"/>
+        <x:v>留空、无电。本方案不用5V轨，不与左+轨桥接。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="46" customHeight="1">
+      <x:c r="A11" s="11" t="str">
+        <x:v>到f8</x:v>
+      </x:c>
       <x:c r="B11" s="13"/>
       <x:c r="C11" s="1">
         <x:v>10</x:v>
@@ -1414,11 +1500,13 @@
         <x:v>动力接法</x:v>
       </x:c>
       <x:c r="T11" s="22" t="str">
-        <x:v>电源正极经保险丝/开关/端子分别到两板 VM；每板功率 GND 独立回公共地端子。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="11"/>
+        <x:v>动力正极经保险丝/物理开关/端子分别到两板VM；每板功率GND独立回公共地端子。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
+      <x:c r="A12" s="11" t="str">
+        <x:v>到f9</x:v>
+      </x:c>
       <x:c r="B12" s="13"/>
       <x:c r="C12" s="1">
         <x:v>11</x:v>
@@ -1443,12 +1531,15 @@
         <x:v>电机线</x:v>
       </x:c>
       <x:c r="T12" s="22" t="str">
-        <x:v>AO1/AO2、BO1/BO2 直接接电机，不经面包板，不将任何输出接地。驱动板固定在面包板旁。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="48" customHeight="1">
+        <x:v>输出直接接各轮电机，不经面包板，不接GND。电机编码器线不能接H桥输出。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="11"/>
-      <x:c r="B13" s="13"/>
+      <x:c r="B13" s="13" t="str">
+        <x:v>公共地
+端子</x:v>
+      </x:c>
       <x:c r="C13" s="1">
         <x:v>12</x:v>
       </x:c>
@@ -1472,10 +1563,10 @@
         <x:v>电压与电流</x:v>
       </x:c>
       <x:c r="T13" s="22" t="str">
-        <x:v>VM 按电机额定值选择，商品模块不超过 12V；尚需核实电机堵转电流是否适合 1.2A 通道。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="48" customHeight="1">
+        <x:v>VM按电机额定值且在模块3–12V范围内选择；核实堵转电流与散热，不能把峰值当持续电流。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="11"/>
       <x:c r="B14" s="13"/>
       <x:c r="C14" s="1">
@@ -1506,10 +1597,10 @@
         <x:v>编码器</x:v>
       </x:c>
       <x:c r="T14" s="22" t="str">
-        <x:v>13/14 排保留 SDA/SCL；VCC 和上拉须先核实模块，不能直接改接 5V。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="48" customHeight="1">
+        <x:v>13/14排保留21/22。AS5600供电及上拉须核实，信号上拉到3.3V；投掷前修复SDA故障。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="11"/>
       <x:c r="B15" s="13"/>
       <x:c r="C15" s="1">
@@ -1540,10 +1631,10 @@
         <x:v>USB 调试</x:v>
       </x:c>
       <x:c r="T15" s="22" t="str">
-        <x:v>ESP32 用 USB 供电时，断开降压输出到 ESP32 5V/VIN 的线，防止两路电源并联。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="48" customHeight="1">
+        <x:v>USB供电时断开降压到ESP32 5V/VIN的线，避免两路电源直接并联。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="46" customHeight="1">
       <x:c r="A16" s="11"/>
       <x:c r="B16" s="13"/>
       <x:c r="C16" s="1">
@@ -1566,13 +1657,13 @@
       <x:c r="P16" s="15"/>
       <x:c r="Q16" s="13"/>
       <x:c r="S16" s="23" t="str">
-        <x:v>固件</x:v>
+        <x:v>固件要求</x:v>
       </x:c>
       <x:c r="T16" s="22" t="str">
-        <x:v>原 QGPMaker/I2C 固件不适用；需 TB6612 四路独立 PWM 固件。接线为规划，未通电验收。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" customHeight="1">
+        <x:v>须适配两线法：PWM波形在IN脚；四个板上PWM脚常高。旧QGPMaker固件不适用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="46" customHeight="1">
       <x:c r="A17" s="11"/>
       <x:c r="B17" s="13"/>
       <x:c r="C17" s="1">
@@ -1595,13 +1686,13 @@
       <x:c r="P17" s="15"/>
       <x:c r="Q17" s="13"/>
       <x:c r="S17" s="23" t="str">
-        <x:v>全车集成</x:v>
+        <x:v>保留原引脚</x:v>
       </x:c>
       <x:c r="T17" s="22" t="str">
-        <x:v>保留投掷与 PS2 时另需 IO 扩展器或第二块主控；当前图为独立底盘方案。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="48" customHeight="1">
+        <x:v>投掷25/26/27/14；PS2 CLK/CS/CMD/DAT=2/4/12/13；AS5600=21/22。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="46" customHeight="1">
       <x:c r="A18" s="11"/>
       <x:c r="B18" s="13"/>
       <x:c r="C18" s="1">
@@ -1624,13 +1715,13 @@
       <x:c r="P18" s="15"/>
       <x:c r="Q18" s="13"/>
       <x:c r="S18" s="23" t="str">
-        <x:v>走线</x:v>
+        <x:v>启动与停止</x:v>
       </x:c>
       <x:c r="T18" s="22" t="str">
-        <x:v>方向/PWM 线按排成束；电机线成对绞合、沿车体两侧走，与编码器线拉开距离。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="36" customHeight="1">
+        <x:v>必须10kΩ下拉。先STBY低、八IN归零，明确使能后拉高；停止/断联/故障撤销使能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="46" customHeight="1">
       <x:c r="A19" s="11"/>
       <x:c r="B19" s="13"/>
       <x:c r="C19" s="1">
@@ -1652,8 +1743,14 @@
       </x:c>
       <x:c r="P19" s="15"/>
       <x:c r="Q19" s="13"/>
-    </x:row>
-    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="S19" s="34" t="str">
+        <x:v>启动配置脚</x:v>
+      </x:c>
+      <x:c r="T19" s="34" t="str">
+        <x:v>15/5以及原PS2的2/12均需实测启动。不能依赖默认上拉制动，STBY保持GPIO33。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="46" customHeight="1">
       <x:c r="A20" s="11"/>
       <x:c r="B20" s="13"/>
       <x:c r="C20" s="1">
@@ -1675,14 +1772,14 @@
       </x:c>
       <x:c r="P20" s="15"/>
       <x:c r="Q20" s="13"/>
-      <x:c r="S20" s="24" t="str">
-        <x:v>资料</x:v>
-      </x:c>
-      <x:c r="T20" s="24" t="str">
-        <x:v>docs/麦轮TB6612接线与面包板排线.md；assets 驱动板图片；东芝 TB6612FNG 数据手册</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="S20" s="34" t="str">
+        <x:v>滑行与制动</x:v>
+      </x:c>
+      <x:c r="T20" s="34" t="str">
+        <x:v>STBY高：IN双低=滑行，双高=短路制动；STBY低=高阻待机，不能机械抱死。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="46" customHeight="1">
       <x:c r="A21" s="11"/>
       <x:c r="B21" s="13"/>
       <x:c r="C21" s="1">
@@ -1704,8 +1801,14 @@
       </x:c>
       <x:c r="P21" s="15"/>
       <x:c r="Q21" s="13"/>
-    </x:row>
-    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="S21" s="34" t="str">
+        <x:v>调速与换向</x:v>
+      </x:c>
+      <x:c r="T21" s="34" t="str">
+        <x:v>正向(PWM,低)，反向(低,PWM)。占空比不等于转速；换向先双低并减速。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="46" customHeight="1">
       <x:c r="A22" s="11"/>
       <x:c r="B22" s="13"/>
       <x:c r="C22" s="1">
@@ -1727,8 +1830,14 @@
       </x:c>
       <x:c r="P22" s="15"/>
       <x:c r="Q22" s="13"/>
-    </x:row>
-    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="S22" s="34" t="str">
+        <x:v>PWM资源</x:v>
+      </x:c>
+      <x:c r="T22" s="34" t="str">
+        <x:v>可为八IN分配PWM；核对SimpleFOC实际后端、通道和定时器，不能只算8+3≤16。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="46" customHeight="1">
       <x:c r="A23" s="11"/>
       <x:c r="B23" s="13"/>
       <x:c r="C23" s="1">
@@ -1750,8 +1859,14 @@
       </x:c>
       <x:c r="P23" s="15"/>
       <x:c r="Q23" s="13"/>
-    </x:row>
-    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="S23" s="34" t="str">
+        <x:v>上电测量</x:v>
+      </x:c>
+      <x:c r="T23" s="34" t="str">
+        <x:v>VM先断开：两板VCC及四PWM约3.3V，两板STBY约0V；再架空、限流逐轮点动。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="46" customHeight="1">
       <x:c r="A24" s="11"/>
       <x:c r="B24" s="13"/>
       <x:c r="C24" s="1">
@@ -1773,8 +1888,14 @@
       </x:c>
       <x:c r="P24" s="15"/>
       <x:c r="Q24" s="13"/>
-    </x:row>
-    <x:row r="25" ht="36" customHeight="1">
+      <x:c r="S24" s="34" t="str">
+        <x:v>迁移旧线</x:v>
+      </x:c>
+      <x:c r="T24" s="34" t="str">
+        <x:v>拆旧GPIO25/26/27/14的PWM线、GPIO4 STBY及e6–f6桥；按新版重排3–9排。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="46" customHeight="1">
       <x:c r="A25" s="11"/>
       <x:c r="B25" s="13"/>
       <x:c r="C25" s="1">
@@ -1796,8 +1917,14 @@
       </x:c>
       <x:c r="P25" s="15"/>
       <x:c r="Q25" s="13"/>
-    </x:row>
-    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="S25" s="34" t="str">
+        <x:v>扩展余量</x:v>
+      </x:c>
+      <x:c r="T25" s="34" t="str">
+        <x:v>现分配不预留新舵机信号GPIO。需要舵机时另作方案；空面包板孔不等于空GPIO。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="46" customHeight="1">
       <x:c r="A26" s="11"/>
       <x:c r="B26" s="13"/>
       <x:c r="C26" s="1">
@@ -1819,8 +1946,14 @@
       </x:c>
       <x:c r="P26" s="15"/>
       <x:c r="Q26" s="13"/>
-    </x:row>
-    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="S26" s="34" t="str">
+        <x:v>走线</x:v>
+      </x:c>
+      <x:c r="T26" s="34" t="str">
+        <x:v>每孔一线；电机线成对绞合并远离编码器。驱动板功率线单独回端子。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="46" customHeight="1">
       <x:c r="A27" s="11"/>
       <x:c r="B27" s="13"/>
       <x:c r="C27" s="1">
@@ -1842,8 +1975,14 @@
       </x:c>
       <x:c r="P27" s="15"/>
       <x:c r="Q27" s="13"/>
-    </x:row>
-    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="S27" s="34" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="T27" s="34" t="str">
+        <x:v>设计已核对，未通电、未烧录、未实物验收。先单测底盘，再集成投掷。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="46" customHeight="1">
       <x:c r="A28" s="11"/>
       <x:c r="B28" s="13"/>
       <x:c r="C28" s="1">
@@ -1865,8 +2004,14 @@
       </x:c>
       <x:c r="P28" s="15"/>
       <x:c r="Q28" s="13"/>
-    </x:row>
-    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="S28" s="34" t="str">
+        <x:v>资料</x:v>
+      </x:c>
+      <x:c r="T28" s="34" t="str">
+        <x:v>麦轮TB6612接线-两线法备选方案.md；麦轮TB6612接线与面包板排线.md；模块商品引脚图。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="46" customHeight="1">
       <x:c r="A29" s="11"/>
       <x:c r="B29" s="13"/>
       <x:c r="C29" s="1">
@@ -1888,8 +2033,14 @@
       </x:c>
       <x:c r="P29" s="15"/>
       <x:c r="Q29" s="13"/>
-    </x:row>
-    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="S29" s="34" t="str">
+        <x:v>芯片依据</x:v>
+      </x:c>
+      <x:c r="T29" s="34" t="str">
+        <x:v>https://toshiba.semicon-storage.com/info/datasheet_en_20141001.pdf?did=10660</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="46" customHeight="1">
       <x:c r="A30" s="11"/>
       <x:c r="B30" s="13"/>
       <x:c r="C30" s="1">
@@ -1911,8 +2062,14 @@
       </x:c>
       <x:c r="P30" s="15"/>
       <x:c r="Q30" s="13"/>
-    </x:row>
-    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="S30" s="34" t="str">
+        <x:v>主控依据</x:v>
+      </x:c>
+      <x:c r="T30" s="34" t="str">
+        <x:v>https://documentation.espressif.com/esp32_datasheet_en.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="46" customHeight="1">
       <x:c r="A31" s="11"/>
       <x:c r="B31" s="13"/>
       <x:c r="C31" s="1">
